--- a/04_Figures/F04_association/modules/T2/group_diff/wilcoxon/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/T2/group_diff/wilcoxon/c_data/results.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="cell" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cell_summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
